--- a/tables/Datas/__enums__.xlsx
+++ b/tables/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
   <si>
     <t>##var</t>
   </si>
@@ -159,6 +159,213 @@
   </si>
   <si>
     <t>已结束</t>
+  </si>
+  <si>
+    <t>Enum.AttributeType</t>
+  </si>
+  <si>
+    <t>HP</t>
+  </si>
+  <si>
+    <t>生命值</t>
+  </si>
+  <si>
+    <t>MP</t>
+  </si>
+  <si>
+    <t>法力值</t>
+  </si>
+  <si>
+    <t>ATTACK</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>DEFENSE</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>SPEED</t>
+  </si>
+  <si>
+    <t>速度</t>
+  </si>
+  <si>
+    <t>CRIT_RATE</t>
+  </si>
+  <si>
+    <r>
+      <t>暴击率（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0~1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>之间的小数）</t>
+    </r>
+  </si>
+  <si>
+    <t>CRIT_DAMAGE</t>
+  </si>
+  <si>
+    <r>
+      <t>暴击伤害倍率（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1.5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>表示暴击</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>150%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伤害）</t>
+    </r>
+  </si>
+  <si>
+    <t>DODGE</t>
+  </si>
+  <si>
+    <t>闪避率</t>
+  </si>
+  <si>
+    <t>HIT</t>
+  </si>
+  <si>
+    <t>命中率</t>
+  </si>
+  <si>
+    <t>MAX_HP</t>
+  </si>
+  <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <t>MAX_MP</t>
+  </si>
+  <si>
+    <t>最大法力值</t>
+  </si>
+  <si>
+    <t>HP_RECOVER</t>
+  </si>
+  <si>
+    <t>生命回复（每秒）</t>
+  </si>
+  <si>
+    <t>MP_RECOVER</t>
+  </si>
+  <si>
+    <t>法力回复（每秒）</t>
+  </si>
+  <si>
+    <t>ATTACK_PERCENT</t>
+  </si>
+  <si>
+    <r>
+      <t>攻击力百分比加成（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>表示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>+10%</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>DEFENSE_PERCENT</t>
+  </si>
+  <si>
+    <t>防御力百分比加成</t>
+  </si>
+  <si>
+    <t>HP_PERCENT</t>
+  </si>
+  <si>
+    <t>生命值百分比加成</t>
+  </si>
+  <si>
+    <t>MP_PERCENT</t>
+  </si>
+  <si>
+    <t>法力值百分比加成</t>
+  </si>
+  <si>
+    <t>SPEED_PERCENT</t>
+  </si>
+  <si>
+    <t>速度百分比加成</t>
   </si>
 </sst>
 </file>
@@ -171,7 +378,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -188,13 +395,21 @@
     <font>
       <i/>
       <sz val="10.5"/>
-      <color rgb="FFC77DBB"/>
-      <name val="Courier New"/>
+      <color theme="1"/>
+      <name val="等线"/>
       <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
-      <color rgb="FF7A7E85"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -341,6 +556,12 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color theme="1"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -678,138 +899,141 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
@@ -818,17 +1042,35 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1149,7 +1391,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1160,183 +1402,196 @@
     <col min="8" max="8" width="13.5083333333333" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
     <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="11" max="11" width="15.125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="1"/>
+      <c r="L3" s="2"/>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4" t="b">
+      <c r="C5" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D5" s="4" t="b">
+      <c r="D5" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J5">
+      <c r="I5" s="9"/>
+      <c r="J5" s="9">
         <v>1</v>
       </c>
+      <c r="K5" s="9"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="H6" t="s">
+      <c r="H6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J6">
+      <c r="I6" s="9"/>
+      <c r="J6" s="9">
         <v>2</v>
       </c>
+      <c r="K6" s="9"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="H7" t="s">
+      <c r="H7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J7">
+      <c r="I7" s="9"/>
+      <c r="J7" s="9">
         <v>3</v>
       </c>
+      <c r="K7" s="9"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="H8" t="s">
+      <c r="H8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="J8">
+      <c r="I8" s="9"/>
+      <c r="J8" s="9">
         <v>4</v>
       </c>
+      <c r="K8" s="9"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="H9" t="s">
+      <c r="H9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="J9">
+      <c r="I9" s="9"/>
+      <c r="J9" s="9">
         <v>5</v>
       </c>
+      <c r="K9" s="9"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="4" t="b">
+      <c r="C10" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D10" s="4" t="b">
+      <c r="D10" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="J10">
+      <c r="I10" s="9"/>
+      <c r="J10" s="9">
         <v>0</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="J11">
+      <c r="I11" s="9"/>
+      <c r="J11" s="9">
         <v>1</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="J12">
+      <c r="I12" s="9"/>
+      <c r="J12" s="9">
         <v>2</v>
       </c>
-      <c r="K12" t="s">
+      <c r="K12" s="8" t="s">
         <v>31</v>
       </c>
     </row>
@@ -1344,41 +1599,44 @@
       <c r="B13" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="4" t="b">
+      <c r="C13" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D13" s="4" t="b">
+      <c r="D13" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
+      <c r="H13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="J13">
+      <c r="I13" s="9"/>
+      <c r="J13" s="9">
         <v>1</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="H14" t="s">
+      <c r="H14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="J14">
+      <c r="I14" s="9"/>
+      <c r="J14" s="9">
         <v>2</v>
       </c>
-      <c r="K14" t="s">
+      <c r="K14" s="8" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="H15" t="s">
+      <c r="H15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="J15">
+      <c r="I15" s="9"/>
+      <c r="J15" s="9">
         <v>3</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="8" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1386,42 +1644,276 @@
       <c r="B16" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="4" t="b">
+      <c r="C16" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="D16" s="4" t="b">
+      <c r="D16" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="J16">
+      <c r="I16" s="9"/>
+      <c r="J16" s="9">
         <v>0</v>
       </c>
-      <c r="K16" s="6" t="s">
+      <c r="K16" s="11" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="17" customFormat="1" spans="8:11">
-      <c r="H17" t="s">
+    <row r="17" customFormat="1" spans="2:11">
+      <c r="H17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="J17">
+      <c r="I17" s="9"/>
+      <c r="J17" s="9">
         <v>1</v>
       </c>
-      <c r="K17" s="6" t="s">
+      <c r="K17" s="11" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="18" customFormat="1" spans="8:11">
-      <c r="H18" t="s">
+    <row r="18" customFormat="1" spans="2:11">
+      <c r="H18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="J18">
+      <c r="I18" s="9"/>
+      <c r="J18" s="9">
         <v>2</v>
       </c>
-      <c r="K18" s="6" t="s">
+      <c r="K18" s="11" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11">
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
+      <c r="K19" s="9"/>
+    </row>
+    <row r="20" spans="2:11">
+      <c r="B20" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9">
+        <v>1</v>
+      </c>
+      <c r="K20" s="12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11">
+      <c r="H21" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9">
+        <v>2</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11">
+      <c r="H22" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9">
+        <v>3</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="H23" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9">
+        <v>4</v>
+      </c>
+      <c r="K23" s="9" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="H24" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9">
+        <v>5</v>
+      </c>
+      <c r="K24" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" ht="27" spans="2:11">
+      <c r="H25" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9">
+        <v>6</v>
+      </c>
+      <c r="K25" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" ht="41.25" spans="2:11">
+      <c r="H26" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9">
+        <v>7</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="H27" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9">
+        <v>8</v>
+      </c>
+      <c r="K27" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="H28" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9">
+        <v>9</v>
+      </c>
+      <c r="K28" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="H29" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9">
+        <v>10</v>
+      </c>
+      <c r="K29" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="H30" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9">
+        <v>11</v>
+      </c>
+      <c r="K30" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="H31" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9">
+        <v>12</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11">
+      <c r="H32" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9">
+        <v>13</v>
+      </c>
+      <c r="K32" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="33" ht="27" spans="8:11">
+      <c r="H33" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9">
+        <v>14</v>
+      </c>
+      <c r="K33" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" ht="27" spans="8:11">
+      <c r="H34" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9">
+        <v>15</v>
+      </c>
+      <c r="K34" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35" spans="8:11">
+      <c r="H35" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9">
+        <v>16</v>
+      </c>
+      <c r="K35" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="36" spans="8:11">
+      <c r="H36" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9">
+        <v>17</v>
+      </c>
+      <c r="K36" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="8:11">
+      <c r="H37" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9">
+        <v>18</v>
+      </c>
+      <c r="K37" s="9" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/tables/Datas/__enums__.xlsx
+++ b/tables/Datas/__enums__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="77">
   <si>
     <t>##var</t>
   </si>
@@ -198,6 +198,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>暴击率（</t>
     </r>
     <r>
@@ -224,6 +230,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>暴击伤害倍率（</t>
     </r>
     <r>
@@ -288,22 +300,16 @@
     <t>最大法力值</t>
   </si>
   <si>
-    <t>HP_RECOVER</t>
-  </si>
-  <si>
-    <t>生命回复（每秒）</t>
-  </si>
-  <si>
-    <t>MP_RECOVER</t>
-  </si>
-  <si>
-    <t>法力回复（每秒）</t>
-  </si>
-  <si>
     <t>ATTACK_PERCENT</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>攻击力百分比加成（</t>
     </r>
     <r>
@@ -1029,7 +1035,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1052,9 +1058,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -1391,7 +1394,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1504,51 +1507,51 @@
       <c r="H5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9">
+      <c r="I5" s="8"/>
+      <c r="J5" s="8">
         <v>1</v>
       </c>
-      <c r="K5" s="9"/>
+      <c r="K5" s="8"/>
     </row>
     <row r="6" spans="1:12">
       <c r="H6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="9">
+      <c r="I6" s="8"/>
+      <c r="J6" s="8">
         <v>2</v>
       </c>
-      <c r="K6" s="9"/>
+      <c r="K6" s="8"/>
     </row>
     <row r="7" spans="1:12">
       <c r="H7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9">
+      <c r="I7" s="8"/>
+      <c r="J7" s="8">
         <v>3</v>
       </c>
-      <c r="K7" s="9"/>
+      <c r="K7" s="8"/>
     </row>
     <row r="8" spans="1:12">
       <c r="H8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9">
+      <c r="I8" s="8"/>
+      <c r="J8" s="8">
         <v>4</v>
       </c>
-      <c r="K8" s="9"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:12">
       <c r="H9" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9">
+      <c r="I9" s="8"/>
+      <c r="J9" s="8">
         <v>5</v>
       </c>
-      <c r="K9" s="9"/>
+      <c r="K9" s="8"/>
     </row>
     <row r="10" spans="1:12">
       <c r="B10" t="s">
@@ -1560,11 +1563,11 @@
       <c r="D10" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9">
+      <c r="I10" s="8"/>
+      <c r="J10" s="8">
         <v>0</v>
       </c>
       <c r="K10" s="8" t="s">
@@ -1572,11 +1575,11 @@
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9">
+      <c r="I11" s="8"/>
+      <c r="J11" s="8">
         <v>1</v>
       </c>
       <c r="K11" s="8" t="s">
@@ -1584,11 +1587,11 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9">
+      <c r="I12" s="8"/>
+      <c r="J12" s="8">
         <v>2</v>
       </c>
       <c r="K12" s="8" t="s">
@@ -1608,8 +1611,8 @@
       <c r="H13" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9">
+      <c r="I13" s="8"/>
+      <c r="J13" s="8">
         <v>1</v>
       </c>
       <c r="K13" s="8" t="s">
@@ -1620,8 +1623,8 @@
       <c r="H14" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9">
+      <c r="I14" s="8"/>
+      <c r="J14" s="8">
         <v>2</v>
       </c>
       <c r="K14" s="8" t="s">
@@ -1632,8 +1635,8 @@
       <c r="H15" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9">
+      <c r="I15" s="8"/>
+      <c r="J15" s="8">
         <v>3</v>
       </c>
       <c r="K15" s="8" t="s">
@@ -1653,11 +1656,11 @@
       <c r="H16" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9">
+      <c r="I16" s="8"/>
+      <c r="J16" s="8">
         <v>0</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="10" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1665,11 +1668,11 @@
       <c r="H17" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9">
+      <c r="I17" s="8"/>
+      <c r="J17" s="8">
         <v>1</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="10" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1677,19 +1680,19 @@
       <c r="H18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9">
+      <c r="I18" s="8"/>
+      <c r="J18" s="8">
         <v>2</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="10" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" spans="2:11">
-      <c r="H19" s="9"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
     </row>
     <row r="20" spans="2:11">
       <c r="B20" t="s">
@@ -1701,14 +1704,14 @@
       <c r="D20" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9">
+      <c r="I20" s="8"/>
+      <c r="J20" s="8">
         <v>1</v>
       </c>
-      <c r="K20" s="12" t="s">
+      <c r="K20" s="11" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1716,204 +1719,180 @@
       <c r="H21" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9">
+      <c r="I21" s="8"/>
+      <c r="J21" s="8">
         <v>2</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="12" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="22" spans="2:11">
-      <c r="H22" s="12" t="s">
+      <c r="H22" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9">
+      <c r="I22" s="8"/>
+      <c r="J22" s="8">
         <v>3</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="23" spans="2:11">
-      <c r="H23" s="12" t="s">
+      <c r="H23" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9">
+      <c r="I23" s="8"/>
+      <c r="J23" s="8">
         <v>4</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K23" s="8" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="24" spans="2:11">
-      <c r="H24" s="12" t="s">
+      <c r="H24" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9">
+      <c r="I24" s="8"/>
+      <c r="J24" s="8">
         <v>5</v>
       </c>
-      <c r="K24" s="13" t="s">
+      <c r="K24" s="12" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="25" ht="27" spans="2:11">
-      <c r="H25" s="12" t="s">
+      <c r="H25" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9">
+      <c r="I25" s="8"/>
+      <c r="J25" s="8">
         <v>6</v>
       </c>
-      <c r="K25" s="13" t="s">
+      <c r="K25" s="12" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="26" ht="41.25" spans="2:11">
-      <c r="H26" s="12" t="s">
+      <c r="H26" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9">
+      <c r="I26" s="8"/>
+      <c r="J26" s="8">
         <v>7</v>
       </c>
-      <c r="K26" s="13" t="s">
+      <c r="K26" s="12" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="27" spans="2:11">
-      <c r="H27" s="12" t="s">
+      <c r="H27" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9">
+      <c r="I27" s="8"/>
+      <c r="J27" s="8">
         <v>8</v>
       </c>
-      <c r="K27" s="13" t="s">
+      <c r="K27" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="28" spans="2:11">
-      <c r="H28" s="12" t="s">
+      <c r="H28" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9">
+      <c r="I28" s="8"/>
+      <c r="J28" s="8">
         <v>9</v>
       </c>
-      <c r="K28" s="13" t="s">
+      <c r="K28" s="12" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="29" spans="2:11">
-      <c r="H29" s="12" t="s">
+      <c r="H29" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9">
+      <c r="I29" s="8"/>
+      <c r="J29" s="8">
         <v>10</v>
       </c>
-      <c r="K29" s="13" t="s">
+      <c r="K29" s="12" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="30" spans="2:11">
-      <c r="H30" s="12" t="s">
+      <c r="H30" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9">
+      <c r="I30" s="8"/>
+      <c r="J30" s="8">
         <v>11</v>
       </c>
-      <c r="K30" s="13" t="s">
+      <c r="K30" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="2:11">
-      <c r="H31" s="12" t="s">
+    <row r="31" ht="27" spans="2:11">
+      <c r="H31" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9">
+      <c r="I31" s="8"/>
+      <c r="J31" s="8">
         <v>12</v>
       </c>
-      <c r="K31" s="13" t="s">
+      <c r="K31" s="12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="32" spans="2:11">
-      <c r="H32" s="12" t="s">
+    <row r="32" ht="27" spans="2:11">
+      <c r="H32" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9">
+      <c r="I32" s="8"/>
+      <c r="J32" s="8">
         <v>13</v>
       </c>
-      <c r="K32" s="13" t="s">
+      <c r="K32" s="12" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" ht="27" spans="8:11">
-      <c r="H33" s="12" t="s">
+    <row r="33" spans="8:11">
+      <c r="H33" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9">
+      <c r="I33" s="8"/>
+      <c r="J33" s="8">
         <v>14</v>
       </c>
-      <c r="K33" s="13" t="s">
+      <c r="K33" s="12" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="34" ht="27" spans="8:11">
-      <c r="H34" s="12" t="s">
+    <row r="34" spans="8:11">
+      <c r="H34" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9">
+      <c r="I34" s="8"/>
+      <c r="J34" s="8">
         <v>15</v>
       </c>
-      <c r="K34" s="13" t="s">
+      <c r="K34" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="35" spans="8:11">
-      <c r="H35" s="12" t="s">
+      <c r="H35" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9">
+      <c r="I35" s="8"/>
+      <c r="J35" s="8">
         <v>16</v>
       </c>
-      <c r="K35" s="13" t="s">
+      <c r="K35" s="8" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="36" spans="8:11">
-      <c r="H36" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9">
-        <v>17</v>
-      </c>
-      <c r="K36" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="37" spans="8:11">
-      <c r="H37" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9">
-        <v>18</v>
-      </c>
-      <c r="K37" s="9" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
